--- a/output/pdf_financials_xlsx/WMS.xlsx
+++ b/output/pdf_financials_xlsx/WMS.xlsx
@@ -2494,19 +2494,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.390951</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.207346</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.401491</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.21654</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.21654</v>
       </c>
     </row>
     <row r="93">
@@ -3968,7 +3968,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4339,7 +4343,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4720,7 +4728,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -5232,7 +5244,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>0.390951</v>
       </c>

--- a/output/pdf_financials_xlsx/WMS.xlsx
+++ b/output/pdf_financials_xlsx/WMS.xlsx
@@ -672,16 +672,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.105888</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.149293</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.03344</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000274</v>
       </c>
     </row>
     <row r="13">
@@ -1022,16 +1022,16 @@
         <v>-0.21048</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.785342</v>
+        <v>-4.89123</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.405158</v>
+        <v>-4.554451</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.960277</v>
+        <v>-2.993717</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.399982</v>
+        <v>-0.400256</v>
       </c>
     </row>
     <row r="28">
@@ -1066,16 +1066,16 @@
         <v>-0.21048</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.785342</v>
+        <v>-4.89123</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.405158</v>
+        <v>-4.554451</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.960277</v>
+        <v>-2.993717</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.399982</v>
+        <v>-0.400256</v>
       </c>
     </row>
     <row r="30">
@@ -1190,7 +1190,7 @@
         <v>0.039944</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.024895</v>
       </c>
     </row>
     <row r="35">
@@ -1234,7 +1234,7 @@
         <v>0.039944</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.024895</v>
       </c>
     </row>
     <row r="37">
@@ -1498,7 +1498,7 @@
         <v>0.0567</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.025301</v>
+        <v>0.000406</v>
       </c>
     </row>
     <row r="49">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3734,7 +3734,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.013528</v>
       </c>
@@ -5775,7 +5779,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>-0.006476</v>
       </c>
@@ -7895,7 +7903,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7979,7 +7987,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8867,7 +8875,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">

--- a/output/pdf_financials_xlsx/WMS.xlsx
+++ b/output/pdf_financials_xlsx/WMS.xlsx
@@ -5898,7 +5898,11 @@
           <t>Proceeds from private placement 5</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6345,7 +6349,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
